--- a/documents/Backlog Tracker/RoamReady_Bug_Todo_Tracker_2026-06-02.xlsx
+++ b/documents/Backlog Tracker/RoamReady_Bug_Todo_Tracker_2026-06-02.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="20" min="1" max="1"/>
@@ -2545,6 +2545,241 @@
       <c r="I39" s="33" t="inlineStr">
         <is>
           <t>Found while debugging the IOS-1 zoom (initially mis-read as a horizontal page-shift). The in-session message bubble &lt;p&gt; (SessionPage.tsx) had whitespace-pre-wrap but no break-words, so a long unbreakable token (URL/long word) could overflow its max-w-[80%] box; overflow leaked through the message list (overflow-y-auto -&gt; overflow-x:visible) into the overflow-hidden chat column. FIX (commit a92f1f9 -&gt; merged 48e18b3, +2/-2): added break-words to the bubble &lt;p&gt; (source fix, wraps long tokens) + min-w-0 to the message-list flex container (guard, can never establish min-content wider than column). Avoided a blunt overflow-x:hidden (would clip tokens mid-word). NOTE: this was correct hygiene but NOT the cause of the reported zoom — that was IOS-1 (font-size). Client tsc &amp;&amp; vite build green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" s="21">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>AUTH-RIG-1</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>Home rig-context row blank on first login/signup until manual refresh</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D40" s="33" t="inlineStr">
+        <is>
+          <t>Auth/Profile</t>
+        </is>
+      </c>
+      <c r="E40" s="34" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="F40" s="36" t="inlineStr">
+        <is>
+          <t>DONE (06-02)</t>
+        </is>
+      </c>
+      <c r="G40" s="33" t="inlineStr">
+        <is>
+          <t>Verify fresh Incognito login</t>
+        </is>
+      </c>
+      <c r="H40" s="33" t="inlineStr">
+        <is>
+          <t>recap 06-02 evening (found in prod-style fresh-login test)</t>
+        </is>
+      </c>
+      <c r="I40" s="33" t="inlineStr">
+        <is>
+          <t>On fresh login the Home screen (SessionPage empty-state) showed NO rig row (rig pill + "2 adults, pets" + hookup + "Planning for your ... — tap the rig to switch"); a manual browser refresh made it appear. Root cause (scouted end-to-end): the login AND signup endpoints return a SLIM user (no rigs, no travelProfile); the FULL user only comes from /users/me via authStore rehydrateUser(), which runs once on App boot — and on fresh login that boot effect already fired and no-opd BEFORE the token existed (it gates on token). So post-login the store held the slim user, Home never re-fetched, and the rig rows conditions were all falsy -&gt; whole row hidden. Refresh works because App remounts with the token now present -&gt; getMe -&gt; setUser(full). Same stale-consumer FAMILY but the flavor is incomplete-data-shape-after-auth, not a re-render miss. FIX (client-only, 2 files +14/-2, commit 70cfc82 -&gt; merged bddd626): await rehydrateUser() right after setToken+setUser in BOTH the login (LoginPage) and signup (SignupPage) success handlers, so the store holds the full /users/me user before navigating to Home. setToken runs first so the token gate passes; rehydrateUser swallows its own errors so a getMe hiccup never bounces the user to login (stays logged in w/ slim user = current behavior, not worse). NO server payload/schema change (deliberately chose client enrich over fattening the login endpoint — avoids an extra join on every login + Tier-1 schema churn). Mirrors AuthCallbackPage (OAuth) which already did getMe post-auth. Client tsc &amp;&amp; vite build green. KEY LEARNING: slim-vs-full user payload shape at the auth boundary — any consumer reading rigs/travelProfile/parties straight off the post-login store will be empty until a refresh; enrich at the auth boundary, not per-consumer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" s="21">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>AUTH-RIG-1</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>Home rig-context row blank on first login/signup until manual refresh</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="inlineStr">
+        <is>
+          <t>Auth/Profile</t>
+        </is>
+      </c>
+      <c r="E41" s="34" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="F41" s="36" t="inlineStr">
+        <is>
+          <t>DONE (06-02)</t>
+        </is>
+      </c>
+      <c r="G41" s="33" t="inlineStr">
+        <is>
+          <t>Verify fresh Incognito login (no refresh)</t>
+        </is>
+      </c>
+      <c r="H41" s="33" t="inlineStr">
+        <is>
+          <t>recap 06-02 evening</t>
+        </is>
+      </c>
+      <c r="I41" s="33" t="inlineStr">
+        <is>
+          <t>On fresh login the Home screen (SessionPage empty-state) showed the greeting + trip box + in-progress trips but NOT the rig context row (rig pill, "2 adults, pets", hookup, "Planning for your &lt;rig&gt; — tap the rig to switch"); a manual browser refresh made it appear. Root cause (scouted end-to-end): the login AND signup endpoints return a SLIM user object (no rigs, no travelProfile); the FULL user only comes from /users/me via authStore rehydrateUser(), which runs once on App boot with empty deps — and on fresh login that boot effect already fired and no-opd BEFORE the token existed (rehydrateUser early-returns without a token). So post-login the store held the slim user, the Home screen never re-fetched, and every rig-row condition was falsy -&gt; whole row hidden. Refresh "fixed" it because App remounts with the token now present -&gt; getMe -&gt; setUser(full). NOT a Zustand re-render issue (selectors re-render fine) — the full data simply never arrived post-auth. FIX (client-only, 2 files +14/-2, commit 70cfc82 -&gt; merged bddd626): await rehydrateUser() after setToken/setUser in BOTH the login (LoginPage) and signup (SignupPage) success handlers, so the store holds rigs+travelProfile before navigating to Home. Chose client enrich over fattening the login payload (avoids touching Tier-1 auth endpoint + Zod schema + an extra DB join on every login). Safe: setToken runs first so rehydrateUsers token gate passes; rehydrateUser swallows its own errors so await never bounces the user to login on a getMe hiccup; no-rig users land cleanly (row stays hidden, no error). Mirrors AuthCallbackPage (OAuth) which already did getMe. Client tsc &amp;&amp; vite build green. KEY LEARNING: slim-vs-full user payload shape at the auth boundary — any consumer reading rigs/travelProfile straight from the post-login store will be empty until a refresh; enrich at the auth boundary, not per-component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" s="21">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>HOME-MOBILE-1</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>Home empty-state mobile polish: open-at-top, trips hint, placeholder clipping, post-login scroll race</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>Bug/Polish</t>
+        </is>
+      </c>
+      <c r="D42" s="33" t="inlineStr">
+        <is>
+          <t>Mobile/UI</t>
+        </is>
+      </c>
+      <c r="E42" s="34" t="inlineStr">
+        <is>
+          <t>P2 — Medium</t>
+        </is>
+      </c>
+      <c r="F42" s="36" t="inlineStr">
+        <is>
+          <t>DONE (06-02)</t>
+        </is>
+      </c>
+      <c r="G42" s="33" t="inlineStr">
+        <is>
+          <t>Verified on device</t>
+        </is>
+      </c>
+      <c r="H42" s="33" t="inlineStr">
+        <is>
+          <t>recap 06-02 evening</t>
+        </is>
+      </c>
+      <c r="I42" s="33" t="inlineStr">
+        <is>
+          <t>Four related Home empty-state (SessionPage) mobile issues, shipped across 3 commits. (1) OPEN-AT-TOP: app used BrowserRouter with no scroll reset, so navigating to Home carried the prior page scrollTop over -&gt; greeting clipped. Fix: new global &lt;ScrollToTop&gt; (useLocation + useLayoutEffect window.scrollTo(0,0) on [pathname]) inside BrowserRouter above Routes (commit 433a1d9 -&gt; ee13d2f). (2) TRIPS HINT: anchoring at top pushes in-progress trips below fold; added muted non-CTA cue at bottom of empty-state column gated on existing showContinueStrip, labeled with live planningTrips.length (commit 9f7b5cd -&gt; 8a871d3). (3) CLIPPED PLACEHOLDER: ChatInput hero textarea rows=1 + fieldSizing:content sizes to empty VALUE not placeholder, so the 2-line placeholder clipped (worsened by the iOS 16px guard wrapping sooner). Fix: minHeight 3.5rem floor (kept fieldSizing/maxHeight so it still grows; no rows=2; copy unchanged) (commit 9f7b5cd). (4) POST-LOGIN SCROLL RACE: greeting still clipped on the post-login landing ONLY. Root cause: global ScrollToTop fires its one pathname-reset while SessionPage is still in its if(hydrating) SPINNER (short page, scroll trivially 0); a tick later hydrating clears, the tall empty-state mounts, browser scroll-anchoring bumps the greeting above the fold, and ScrollToTop never re-fires. From-Dashboard worked because warm data collapses spinner-&gt;content into ~the reset frame; post-login is COLD (awaited getMe + fresh-session POST + session fetch) so the gap is wide. NOTE: today AUTH-RIG-1 added an awaited rehydrateUser() to login, which WIDENED the cold path and is what exposed this race. Fix: SessionPage-local useLayoutEffect window.scrollTo(0,0) guarded on the hydrating-&gt;ready edge (dep [hydrating], !hydrating), re-applying the reset at the moment real content first paints; useLayoutEffect = before paint = no jump (commit eb61a4d -&gt; 33a7748). Safe for active chat: window reset != the internal overflow-y-auto message-list scroll (bottomRef), different containers. All client tsc &amp;&amp; vite build green. KEY LEARNING: a global pathname-keyed scroll reset MISSES content that mounts after an async hydrating gate; pages with a hydrating spinner need a LOCAL re-reset on the ready edge. Also: stale-bundle on the phone (restart Vite + hard-clear) masked test results repeatedly tonight — always confirm fresh bundle before judging a mobile fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" s="21">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>SCROLL-BEHAVIOR-1</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>Conversation over-scroll (top/controls clipped) + shared scroll-reset hook</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>Bug/Refactor</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="inlineStr">
+        <is>
+          <t>Mobile/UI</t>
+        </is>
+      </c>
+      <c r="E43" s="34" t="inlineStr">
+        <is>
+          <t>P2 — Medium</t>
+        </is>
+      </c>
+      <c r="F43" s="36" t="inlineStr">
+        <is>
+          <t>DONE (06-02) — Pattern-1 rollout PENDING</t>
+        </is>
+      </c>
+      <c r="G43" s="33" t="inlineStr">
+        <is>
+          <t>Verified short+long convo on device</t>
+        </is>
+      </c>
+      <c r="H43" s="33" t="inlineStr">
+        <is>
+          <t>recap 06-02 evening (app-wide scroll audit)</t>
+        </is>
+      </c>
+      <c r="I43" s="33" t="inlineStr">
+        <is>
+          <t>Reported: in the active conversation view, an AI reply scrolled the top of the page (incl. the New trip / Cancel this plan controls) off-screen even when the exchange already fit. App-wide scroll audit found this is a CLASS of bug with two patterns. PATTERN 2 (over-scroll on content change): SessionPage bottomRef.scrollIntoView (and ModifyTripPanel) used default block:start, which scrolls ALL scrollable ancestors incl. the window on mobile (dvh &gt; visual viewport), carrying the non-sticky header off the top even when nothing needed scrolling. FIX (commit 32ad9df -&gt; merged 8c2097d): block:nearest on both call sites — no-ops when the latest message is already visible (short exchange stays put) but still scrolls minimum to reveal the newest message in long convos (scroll-to-latest preserved). TripBookingPage scrollToStop left alone (intentional deep-link nav). PATTERN 1 (pre-scroll on arrival): the global ScrollToTop fires window.scrollTo(0,0) on [pathname] only, so it MISSES content that mounts after an async hydrating/loading gate (the cold post-login clip — see HOME-MOBILE-1). Audit found ~15 pages with a short-loader-&gt;tall-content gate that lack a local ready-edge reset (Dashboard, TripSummary, TripJournal, PackingList, SharedTrip, EditRig, TravelParty, OHV/Van/CarCamping/Roadmap/Maintenance, admin). Established the canonical fix: new hook client/src/hooks/useScrollResetOnReady.ts (useLayoutEffect(()=&gt;{ if(ready) window.scrollTo(0,0) },[ready])); refactored SessionPage onto useScrollResetOnReady(!hydrating) — behavior-identical, no runtime change (commit 8e1fdd6 -&gt; merged aaa75fe). Both client tsc &amp;&amp; vite build green. PENDING (held deliberately, fresh-head pass): roll useScrollResetOnReady(!loading) out to the ~15 candidate pages — one line per page, mechanical, but deserves its own focused test sweep; mostly PREVENTIVE (not all candidates will reproduce — needs scroll-anchoring to inject above the fold). KEY LEARNING: a global pathname-keyed scroll reset misses post-hydration content; any page with a loading spinner before tall content needs a local ready-edge reset — now centralized in useScrollResetOnReady so it is not sprinkled/drifting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" s="21">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>DATE-ANCHOR-1</t>
+        </is>
+      </c>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>Trips ignore user departure date; every itinerary anchors to today</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>AI/Trip pipeline</t>
+        </is>
+      </c>
+      <c r="E44" s="34" t="inlineStr">
+        <is>
+          <t>P1 — High</t>
+        </is>
+      </c>
+      <c r="F44" s="36" t="inlineStr">
+        <is>
+          <t>DONE (06-02)</t>
+        </is>
+      </c>
+      <c r="G44" s="33" t="inlineStr">
+        <is>
+          <t>Verified specific + vague-month in fresh session</t>
+        </is>
+      </c>
+      <c r="H44" s="33" t="inlineStr">
+        <is>
+          <t>recap 06-02 evening (gated audit + build)</t>
+        </is>
+      </c>
+      <c r="I44" s="33" t="inlineStr">
+        <is>
+          <t>SYSTEMIC: every trip anchored its itinerary to TODAY regardless of the date the user gave (confirmed across multiple users/trips incl. ones with explicit dates). Example: a September trip rendered Day 1 = Jun 4 (build day); season survived only in the trip NAME ("...Fall Adventure"). Root cause (gated scout, root cause (a) = never captured): the itinerary JSON schema the AI emits had NO date field, so a stated date had nowhere structured to land; promote wrote no Trip.startDate; server recomputeStopDates fell back through trip.startDate ?? firstDatedStop.arrivalDate ?? new Date() -&gt; today, and back-filled startDate + every stop arrivalDate to today. The DISPLAY was innocent (correctly read the stored dates, which were today). KEY AUDIT FINDING: the whole server side was already wired right — PlanningSessionPromoteSchema already accepted startDate, promoteSession spreads ...data, recomputeStopDates anchors on startDate, and the map-page shiftDates picker already re-anchors all stops. The pipeline just never RECEIVED a date. FIX (gated 2-phase, +12 across 2 files, commit 5c400b7 -&gt; merged 00b59d7): (1) services/ai.ts — added top-level startDate (ISO yyyy-mm-dd) to the itinerary JSON schema; added a DEPARTURE DATE RULE: specific date -&gt; resolve+emit; vague month/season -&gt; propose FIRST TUESDAY of that month (best midweek RV travel: lighter weekend traffic, easier campground availability) and ASK to confirm, emitting NO &lt;itinerary&gt; that turn (mirrors surprise-rule STEP 1 so the build does not trip early); no date -&gt; omit. Also injected "Today is &lt;ISO date&gt;." into the system prompt so the AI resolves the correct YEAR (LLM date-guessing is unreliable — this was the gap that would have silently broken vague-month + specific-date year resolution). (2) SessionPage.tsx buildItinerary — added startDate: itinerary.startDate ?? null to the promote payload (the single client wiring line). No server/schema change needed; no backfill of existing trips (decided: leave them, fix new only); display ?? new Date() fallback left intact. Server tsc + client tsc/vite build green. DESIGN DECISIONS: vague month -&gt; first Tuesday + confirm; editable post-build via existing map-page date picker; existing wrong-dated trips left as-is. KEY LEARNING: a feature can look like a 4-layer rebuild but be a capture-only gap — audit-first (gated) revealed the server was already ready and the real fix was 1 schema field + 1 prompt rule + 1 client line. Also: any AI feature that must reason about dates needs today injected into the prompt — never trust the model to know the current date/year.</t>
         </is>
       </c>
     </row>
